--- a/analysis/TEST/CBATCH.v2.0.0.xlsx
+++ b/analysis/TEST/CBATCH.v2.0.0.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10911"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/TEST/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33854F30-A890-A74C-AF82-4F16321DB2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66319340-705F-7C4D-8D6E-CE6849CDE4FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6460" yWindow="1580" windowWidth="23220" windowHeight="14800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6460" yWindow="1580" windowWidth="23220" windowHeight="14800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
-    <sheet name="Plate" sheetId="2" r:id="rId2"/>
+    <sheet name="Sample IDs" sheetId="2" r:id="rId2"/>
     <sheet name="Comments" sheetId="3" r:id="rId3"/>
     <sheet name="Lists" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -382,8 +382,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -402,7 +402,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -411,7 +411,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -424,14 +424,11 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -849,10 +846,10 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="19"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -879,10 +876,10 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="1">
         <v>10</v>
       </c>
       <c r="C8" s="1"/>
@@ -943,10 +940,10 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C10" s="1"/>
@@ -975,10 +972,10 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="1"/>
@@ -32993,7 +32990,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="7" t="s">
